--- a/공덕표/화두_공덕표.xlsx
+++ b/공덕표/화두_공덕표.xlsx
@@ -25,7 +25,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>하루 전체 상한 21,600 = 연꽃 한 송이 · 2026-10-10 기준</t>
+          <t>하루 전체 상한 21,600 = 연꽃 한 송이 · 2026-10-13 기준</t>
         </is>
       </c>
     </row>
@@ -84,7 +84,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -92,19 +92,19 @@
         </is>
       </c>
       <c r="E5">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="F5">
-        <v>19440</v>
+        <v>21600</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>695회</t>
+          <t>675회</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 45분</t>
         </is>
       </c>
     </row>
@@ -120,7 +120,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -128,19 +128,19 @@
         </is>
       </c>
       <c r="E6">
-        <v>504</v>
+        <v>390</v>
       </c>
       <c r="F6">
-        <v>9720</v>
+        <v>21600</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>116회</t>
+          <t>333회</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 55분</t>
         </is>
       </c>
     </row>
@@ -167,16 +167,16 @@
         <v>432</v>
       </c>
       <c r="F7">
-        <v>16200</v>
+        <v>21600</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75회</t>
+          <t>100회</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 50분</t>
         </is>
       </c>
     </row>
@@ -192,7 +192,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -200,19 +200,19 @@
         </is>
       </c>
       <c r="E8">
-        <v>900</v>
+        <v>375</v>
       </c>
       <c r="F8">
-        <v>43200</v>
+        <v>21600</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3,600회</t>
+          <t>4,320회</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>약 24분</t>
+          <t>약 58분</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -236,10 +236,10 @@
         </is>
       </c>
       <c r="E9">
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="F9">
-        <v>43200</v>
+        <v>21600</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -248,7 +248,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>약 30분</t>
+          <t>약 1.0시간</t>
         </is>
       </c>
     </row>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -272,19 +272,19 @@
         </is>
       </c>
       <c r="E10">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="F10">
-        <v>43200</v>
+        <v>21600</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3,600회</t>
+          <t>4,320회</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>약 30분</t>
+          <t>약 1.2시간</t>
         </is>
       </c>
     </row>
@@ -300,7 +300,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -308,19 +308,19 @@
         </is>
       </c>
       <c r="E11">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="F11">
-        <v>4860</v>
+        <v>21600</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>58회</t>
+          <t>240회</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 1.0시간</t>
         </is>
       </c>
     </row>
@@ -336,7 +336,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>2160</v>
+        <v>8640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -344,19 +344,19 @@
         </is>
       </c>
       <c r="E12">
-        <v>108</v>
+        <v>432</v>
       </c>
       <c r="F12">
-        <v>10800</v>
+        <v>21600</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5회</t>
+          <t>3회</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 50분</t>
         </is>
       </c>
     </row>
@@ -372,7 +372,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>432</v>
+        <v>780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -380,19 +380,19 @@
         </is>
       </c>
       <c r="E13">
-        <v>216</v>
+        <v>390</v>
       </c>
       <c r="F13">
-        <v>4320</v>
+        <v>21600</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10회</t>
+          <t>28회</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 55분</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -416,19 +416,19 @@
         </is>
       </c>
       <c r="E14">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="F14">
-        <v>6300</v>
+        <v>21600</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>38회</t>
+          <t>75회</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 1.3시간</t>
         </is>
       </c>
     </row>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>1296</v>
+        <v>432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -452,19 +452,19 @@
         </is>
       </c>
       <c r="E15">
-        <v>1296</v>
+        <v>432</v>
       </c>
       <c r="F15">
-        <v>6480</v>
+        <v>21600</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5회</t>
+          <t>50회</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 50분</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>864</v>
+        <v>520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="E16">
-        <v>720</v>
+        <v>433</v>
       </c>
       <c r="F16">
-        <v>43200</v>
+        <v>21600</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50회</t>
+          <t>42회</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>약 30분</t>
+          <t>약 50분</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>432</v>
+        <v>1180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -524,19 +524,19 @@
         </is>
       </c>
       <c r="E17">
-        <v>144</v>
+        <v>393</v>
       </c>
       <c r="F17">
-        <v>6480</v>
+        <v>21600</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15회</t>
+          <t>19회</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>혼자서는 못 채움</t>
+          <t>약 55분</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>432</v>
+        <v>2160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -560,14 +560,14 @@
         </is>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="F18">
-        <v>4320</v>
+        <v>2160</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10회</t>
+          <t>1회</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="F19">
-        <v>8640</v>
+        <v>2160</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20회</t>
+          <t>5회</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -637,11 +637,11 @@
         <v>126</v>
       </c>
       <c r="F20">
-        <v>3240</v>
+        <v>1680</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>39회</t>
+          <t>20회</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F21">
-        <v>8640</v>
+        <v>2160</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>40회</t>
+          <t>10회</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -711,11 +711,11 @@
         <v>36</v>
       </c>
       <c r="F22">
-        <v>1620</v>
+        <v>720</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>45회</t>
+          <t>20회</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5회</t>
+          <t>1회</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
         </is>
       </c>
       <c r="F24">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10회</t>
+          <t>5회</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
